--- a/public/assets/template-excel/odp.xlsx
+++ b/public/assets/template-excel/odp.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>Nama Area</t>
+    <t>Cabang</t>
   </si>
   <si>
     <t>Nama ODP</t>
@@ -44,7 +44,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -52,29 +52,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -83,14 +71,11 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -306,38 +291,37 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.13"/>
-    <col customWidth="1" min="4" max="4" width="19.25"/>
-    <col customWidth="1" min="7" max="7" width="17.5"/>
-    <col customWidth="1" min="8" max="8" width="19.0"/>
+    <col customWidth="1" min="4" max="4" width="17.0"/>
+    <col customWidth="1" min="7" max="7" width="15.63"/>
+    <col customWidth="1" min="8" max="8" width="16.13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
